--- a/LCAResults/SCPLCA_TornadoPlotResults.xlsx
+++ b/LCAResults/SCPLCA_TornadoPlotResults.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://api.box.com/wopi/files/2410759197043/WOPIServiceId_TP_BOX_2/WOPIUserId_-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="210" documentId="8_{8EA4217A-382B-4A71-8E27-3811332F815A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E210A0A-77F8-4E73-90F3-48A9D074F147}"/>
+  <xr:revisionPtr revIDLastSave="269" documentId="8_{8EA4217A-382B-4A71-8E27-3811332F815A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD85251B-5224-467F-8CF5-4E9766142F0A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{7CE15DA7-D44F-409E-B74A-9F763C658849}"/>
+    <workbookView xWindow="-14400" yWindow="0" windowWidth="14400" windowHeight="15600" activeTab="1" xr2:uid="{7CE15DA7-D44F-409E-B74A-9F763C658849}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -150,9 +150,6 @@
     <t>Nutrients Demand</t>
   </si>
   <si>
-    <t>Steam Demand</t>
-  </si>
-  <si>
     <t>Substrate Intensity</t>
   </si>
   <si>
@@ -169,6 +166,9 @@
   </si>
   <si>
     <t>+100%</t>
+  </si>
+  <si>
+    <t>Natural Gas Demand</t>
   </si>
 </sst>
 </file>
@@ -820,16 +820,16 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" t="s">
         <v>38</v>
       </c>
-      <c r="D2" t="s">
-        <v>39</v>
-      </c>
       <c r="F2">
-        <v>31.7</v>
+        <v>11.2</v>
       </c>
       <c r="G2">
-        <v>31.7</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -840,16 +840,16 @@
         <v>3</v>
       </c>
       <c r="C3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" t="s">
         <v>38</v>
       </c>
-      <c r="D3" t="s">
-        <v>39</v>
-      </c>
       <c r="F3">
-        <v>74.900000000000006</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>74.900000000000006</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -860,16 +860,16 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" t="s">
         <v>38</v>
       </c>
-      <c r="D4" t="s">
-        <v>39</v>
-      </c>
       <c r="F4">
-        <v>517.70000000000005</v>
+        <v>110.9</v>
       </c>
       <c r="G4">
-        <v>517.70000000000005</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -880,10 +880,10 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
         <v>38</v>
-      </c>
-      <c r="D5" t="s">
-        <v>39</v>
       </c>
       <c r="F5">
         <v>185</v>
@@ -903,19 +903,19 @@
         <v>-0.5</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F6">
-        <v>31.4</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>31.7</v>
+        <v>11.2</v>
       </c>
       <c r="H6">
-        <v>32</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -929,19 +929,19 @@
         <v>-0.5</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F7">
-        <v>74.7</v>
+        <v>20.8</v>
       </c>
       <c r="G7">
-        <v>74.900000000000006</v>
+        <v>21</v>
       </c>
       <c r="H7">
-        <v>75.2</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -955,19 +955,19 @@
         <v>-0.5</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F8">
-        <v>516.4</v>
+        <v>109.8</v>
       </c>
       <c r="G8">
-        <v>517.70000000000005</v>
+        <v>111</v>
       </c>
       <c r="H8">
-        <v>519</v>
+        <v>112.3</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -981,10 +981,10 @@
         <v>-0.5</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9">
         <v>98</v>
@@ -1007,19 +1007,19 @@
         <v>-0.5</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F10">
-        <v>20.8</v>
+        <v>10.5</v>
       </c>
       <c r="G10">
-        <v>31.7</v>
+        <v>11.2</v>
       </c>
       <c r="H10">
-        <v>42.7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -1033,19 +1033,19 @@
         <v>-0.5</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F11">
-        <v>46.1</v>
+        <v>19.2</v>
       </c>
       <c r="G11">
-        <v>74.900000000000006</v>
+        <v>21</v>
       </c>
       <c r="H11">
-        <v>104</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1059,19 +1059,19 @@
         <v>-0.5</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F12">
-        <v>299.89999999999998</v>
+        <v>96.6</v>
       </c>
       <c r="G12">
-        <v>517.70000000000005</v>
+        <v>111</v>
       </c>
       <c r="H12">
-        <v>735.4</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1085,19 +1085,19 @@
         <v>-0.5</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F13">
-        <v>186.9</v>
+        <v>187</v>
       </c>
       <c r="G13">
         <v>187</v>
       </c>
       <c r="H13">
-        <v>187.3</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1111,19 +1111,19 @@
         <v>-0.5</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F14">
-        <v>31.4</v>
+        <v>11</v>
       </c>
       <c r="G14">
-        <v>31.7</v>
+        <v>11.2</v>
       </c>
       <c r="H14">
-        <v>32</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -1137,19 +1137,19 @@
         <v>-0.5</v>
       </c>
       <c r="D15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F15">
-        <v>74.599999999999994</v>
+        <v>20.8</v>
       </c>
       <c r="G15">
-        <v>74.900000000000006</v>
+        <v>21</v>
       </c>
       <c r="H15">
-        <v>75.2</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1163,19 +1163,19 @@
         <v>-0.5</v>
       </c>
       <c r="D16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F16">
-        <v>517.4</v>
+        <v>110.7</v>
       </c>
       <c r="G16">
-        <v>517.70000000000005</v>
+        <v>111</v>
       </c>
       <c r="H16">
-        <v>518</v>
+        <v>111.3</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1189,24 +1189,24 @@
         <v>-0.5</v>
       </c>
       <c r="D17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F17">
-        <v>186.8</v>
+        <v>186.5</v>
       </c>
       <c r="G17">
         <v>187</v>
       </c>
       <c r="H17">
-        <v>187.3</v>
+        <v>187.8</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
@@ -1215,24 +1215,24 @@
         <v>0</v>
       </c>
       <c r="D18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F18">
         <v>9.8000000000000007</v>
       </c>
       <c r="G18">
-        <v>31.7</v>
+        <v>11.2</v>
       </c>
       <c r="H18">
-        <v>53.7</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B19" t="s">
         <v>3</v>
@@ -1241,24 +1241,24 @@
         <v>0</v>
       </c>
       <c r="D19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F19">
         <v>17.3</v>
       </c>
       <c r="G19">
-        <v>74.900000000000006</v>
+        <v>21</v>
       </c>
       <c r="H19">
-        <v>133</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B20" t="s">
         <v>4</v>
@@ -1267,24 +1267,24 @@
         <v>0</v>
       </c>
       <c r="D20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F20">
         <v>82.2</v>
       </c>
       <c r="G20">
-        <v>517.70000000000005</v>
+        <v>111</v>
       </c>
       <c r="H20">
-        <v>953.2</v>
+        <v>139.80000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B21" t="s">
         <v>5</v>
@@ -1293,24 +1293,24 @@
         <v>0</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F21">
-        <v>186.8</v>
+        <v>187</v>
       </c>
       <c r="G21">
         <v>187</v>
       </c>
       <c r="H21">
-        <v>187.4</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
         <v>2</v>
@@ -1319,24 +1319,24 @@
         <v>-0.5</v>
       </c>
       <c r="D22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F22">
-        <v>29</v>
+        <v>8.5</v>
       </c>
       <c r="G22">
-        <v>31.7</v>
+        <v>11.2</v>
       </c>
       <c r="H22">
-        <v>34.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B23" t="s">
         <v>3</v>
@@ -1345,24 +1345,24 @@
         <v>-0.5</v>
       </c>
       <c r="D23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F23">
-        <v>67.7</v>
+        <v>13.8</v>
       </c>
       <c r="G23">
-        <v>74.900000000000006</v>
+        <v>21</v>
       </c>
       <c r="H23">
-        <v>82.2</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" t="s">
         <v>4</v>
@@ -1371,24 +1371,24 @@
         <v>-0.5</v>
       </c>
       <c r="D24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F24">
-        <v>485.7</v>
+        <v>79</v>
       </c>
       <c r="G24">
-        <v>517.70000000000005</v>
+        <v>111</v>
       </c>
       <c r="H24">
-        <v>549.5</v>
+        <v>142.80000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B25" t="s">
         <v>5</v>
@@ -1397,10 +1397,10 @@
         <v>-0.5</v>
       </c>
       <c r="D25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F25">
         <v>187</v>
